--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6857" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6855" uniqueCount="699">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
+    <t>Extension</t>
   </si>
   <si>
     <t>Extension for indicating the context.</t>
@@ -713,6 +713,9 @@
     <t>Medication.extension.extension</t>
   </si>
   <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>Medication.extension:drugCategory.url</t>
   </si>
   <si>
@@ -852,9 +855,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -944,6 +944,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>Information on the packaging of a formulation.</t>
   </si>
   <si>
@@ -955,9 +958,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-manufacturing-instructions-extension}
 </t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>Manufacturing instructions regarding the preparation of a formulation (Subscriptio).</t>
@@ -1178,6 +1178,9 @@
   </si>
   <si>
     <t>Medication.code.coding.display</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Medication.code.coding:pzn.userSelected</t>
@@ -4726,7 +4729,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -4842,7 +4845,7 @@
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4958,7 +4961,7 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
@@ -5074,7 +5077,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -5204,7 +5207,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5226,14 +5229,12 @@
         <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -5300,7 +5301,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -5311,10 +5312,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5340,13 +5341,13 @@
         <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5354,7 +5355,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -5396,7 +5397,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -5425,10 +5426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5454,10 +5455,10 @@
         <v>148</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5484,11 +5485,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5506,7 +5507,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5515,7 +5516,7 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
@@ -5535,10 +5536,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5647,10 +5648,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5761,10 +5762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5790,16 +5791,16 @@
         <v>130</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5848,7 +5849,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5866,21 +5867,21 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5906,13 +5907,13 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5962,7 +5963,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5980,21 +5981,21 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6020,14 +6021,14 @@
         <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6076,7 +6077,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6094,21 +6095,21 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6134,14 +6135,12 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N32" t="s" s="2">
         <v>268</v>
       </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>269</v>
       </c>
@@ -6682,7 +6681,7 @@
         <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6708,13 +6707,13 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6764,7 +6763,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6796,7 +6795,7 @@
         <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6822,10 +6821,10 @@
         <v>173</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6852,7 +6851,7 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
@@ -6874,7 +6873,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6934,10 +6933,10 @@
         <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>112</v>
@@ -7019,13 +7018,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>108</v>
@@ -7047,10 +7046,10 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>301</v>
+        <v>203</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>302</v>
@@ -7240,7 +7239,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -8538,16 +8537,16 @@
         <v>130</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8596,7 +8595,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8614,13 +8613,13 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8654,13 +8653,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8710,7 +8709,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8728,13 +8727,13 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55">
@@ -8775,7 +8774,7 @@
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8824,7 +8823,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8842,13 +8841,13 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56">
@@ -8882,13 +8881,13 @@
         <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>269</v>
@@ -8969,10 +8968,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9085,13 +9084,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>345</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>78</v>
@@ -9135,7 +9134,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9203,7 +9202,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>357</v>
@@ -9315,7 +9314,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>359</v>
@@ -9429,7 +9428,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>361</v>
@@ -9458,16 +9457,16 @@
         <v>130</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9516,7 +9515,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9534,18 +9533,18 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>363</v>
@@ -9574,13 +9573,13 @@
         <v>102</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9630,7 +9629,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9648,18 +9647,18 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>365</v>
@@ -9695,7 +9694,7 @@
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9744,7 +9743,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9762,18 +9761,18 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>369</v>
@@ -9802,13 +9801,13 @@
         <v>102</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>269</v>
@@ -9889,10 +9888,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10005,13 +10004,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>345</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>78</v>
@@ -10055,7 +10054,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10123,7 +10122,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>357</v>
@@ -10235,7 +10234,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>359</v>
@@ -10349,7 +10348,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>361</v>
@@ -10378,16 +10377,16 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10436,7 +10435,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10454,18 +10453,18 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>363</v>
@@ -10494,13 +10493,13 @@
         <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10550,7 +10549,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10568,18 +10567,18 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>365</v>
@@ -10615,7 +10614,7 @@
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10664,7 +10663,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10682,18 +10681,18 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>369</v>
@@ -10722,13 +10721,13 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>269</v>
@@ -10809,10 +10808,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10925,10 +10924,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10954,16 +10953,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -11012,7 +11011,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11030,21 +11029,21 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11070,13 +11069,13 @@
         <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11102,13 +11101,13 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -11126,7 +11125,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11144,7 +11143,7 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -11155,10 +11154,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11181,16 +11180,16 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11240,7 +11239,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11252,27 +11251,27 @@
         <v>156</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11381,10 +11380,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11495,10 +11494,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11524,13 +11523,13 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11580,7 +11579,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11589,7 +11588,7 @@
         <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>100</v>
@@ -11609,10 +11608,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11638,13 +11637,13 @@
         <v>130</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11673,10 +11672,10 @@
         <v>152</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11694,7 +11693,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11723,10 +11722,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11752,13 +11751,13 @@
         <v>314</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11808,7 +11807,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11826,7 +11825,7 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11837,10 +11836,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11866,13 +11865,13 @@
         <v>102</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11922,7 +11921,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11951,10 +11950,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11980,13 +11979,13 @@
         <v>333</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12015,10 +12014,10 @@
         <v>163</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -12036,7 +12035,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12051,24 +12050,24 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12177,10 +12176,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12291,13 +12290,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="B86" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="C86" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>108</v>
@@ -12319,13 +12318,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>112</v>
@@ -12396,7 +12395,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12407,10 +12406,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12521,13 +12520,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="B88" t="s" s="2">
-        <v>460</v>
-      </c>
       <c r="C88" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -12558,7 +12557,7 @@
         <v>347</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>349</v>
@@ -12571,7 +12570,7 @@
         <v>78</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>78</v>
@@ -12586,11 +12585,11 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12637,10 +12636,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12749,10 +12748,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12863,10 +12862,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12892,16 +12891,16 @@
         <v>130</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12950,7 +12949,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12968,21 +12967,21 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13008,13 +13007,13 @@
         <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13064,7 +13063,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13082,21 +13081,21 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13129,7 +13128,7 @@
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13178,7 +13177,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13196,21 +13195,21 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13236,13 +13235,13 @@
         <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>269</v>
@@ -13323,10 +13322,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13439,13 +13438,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
@@ -13489,7 +13488,7 @@
         <v>78</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>78</v>
@@ -13504,11 +13503,11 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -13555,10 +13554,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13667,10 +13666,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13781,10 +13780,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13810,16 +13809,16 @@
         <v>130</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13868,7 +13867,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13886,21 +13885,21 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13926,13 +13925,13 @@
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13982,7 +13981,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14000,21 +13999,21 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14047,7 +14046,7 @@
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14096,7 +14095,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14114,21 +14113,21 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14154,13 +14153,13 @@
         <v>102</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>269</v>
@@ -14241,10 +14240,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14357,10 +14356,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14386,16 +14385,16 @@
         <v>102</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14444,7 +14443,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14462,21 +14461,21 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14499,16 +14498,16 @@
         <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14558,7 +14557,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14570,13 +14569,13 @@
         <v>156</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14587,10 +14586,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14699,10 +14698,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14813,10 +14812,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14839,16 +14838,16 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14878,7 +14877,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -14896,7 +14895,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14908,27 +14907,27 @@
         <v>156</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15037,10 +15036,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15151,13 +15150,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>108</v>
@@ -15179,13 +15178,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>112</v>
@@ -15267,13 +15266,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>108</v>
@@ -15295,13 +15294,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>203</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>112</v>
@@ -15372,7 +15371,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15383,10 +15382,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15409,19 +15408,19 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15470,7 +15469,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15488,21 +15487,21 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15528,20 +15527,20 @@
         <v>173</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R114" t="s" s="2">
         <v>78</v>
@@ -15562,13 +15561,13 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15586,7 +15585,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15604,21 +15603,21 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15644,16 +15643,16 @@
         <v>102</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15702,7 +15701,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15720,21 +15719,21 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15760,16 +15759,16 @@
         <v>130</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15818,7 +15817,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15827,7 +15826,7 @@
         <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>100</v>
@@ -15836,21 +15835,21 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15876,16 +15875,16 @@
         <v>173</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15934,7 +15933,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15952,21 +15951,21 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15989,16 +15988,16 @@
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16028,7 +16027,7 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>78</v>
@@ -16046,7 +16045,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16058,27 +16057,27 @@
         <v>156</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16187,10 +16186,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16301,10 +16300,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16327,19 +16326,19 @@
         <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -16388,7 +16387,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16406,21 +16405,21 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16446,20 +16445,20 @@
         <v>173</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q122" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R122" t="s" s="2">
         <v>78</v>
@@ -16480,13 +16479,13 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16504,7 +16503,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16522,21 +16521,21 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16562,16 +16561,16 @@
         <v>102</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16620,7 +16619,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16638,21 +16637,21 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16678,16 +16677,16 @@
         <v>130</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16736,7 +16735,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16745,7 +16744,7 @@
         <v>88</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>100</v>
@@ -16754,21 +16753,21 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16794,16 +16793,16 @@
         <v>173</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16852,7 +16851,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16870,21 +16869,21 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16907,16 +16906,16 @@
         <v>78</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16966,7 +16965,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16984,7 +16983,7 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
@@ -16995,10 +16994,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17107,10 +17106,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17221,13 +17220,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="B129" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="C129" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>78</v>
@@ -17249,13 +17248,13 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17335,14 +17334,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17364,10 +17363,10 @@
         <v>109</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>112</v>
@@ -17422,7 +17421,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17451,10 +17450,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17477,17 +17476,17 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17524,7 +17523,7 @@
         <v>78</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AC131" s="2"/>
       <c r="AD131" t="s" s="2">
@@ -17534,7 +17533,7 @@
         <v>142</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>88</v>
@@ -17552,24 +17551,24 @@
         <v>339</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>78</v>
@@ -17594,14 +17593,14 @@
         <v>333</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17650,7 +17649,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>88</v>
@@ -17668,21 +17667,21 @@
         <v>339</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17791,10 +17790,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17905,10 +17904,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18019,13 +18018,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="B136" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="C136" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>78</v>
@@ -18069,7 +18068,7 @@
         <v>78</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>78</v>
@@ -18137,10 +18136,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18249,10 +18248,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18363,10 +18362,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18392,16 +18391,16 @@
         <v>130</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18450,7 +18449,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18468,21 +18467,21 @@
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18508,13 +18507,13 @@
         <v>102</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18564,7 +18563,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18582,21 +18581,21 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18629,7 +18628,7 @@
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18678,7 +18677,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -18696,21 +18695,21 @@
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18736,13 +18735,13 @@
         <v>102</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>269</v>
@@ -18823,10 +18822,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18939,13 +18938,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>78</v>
@@ -18989,7 +18988,7 @@
         <v>78</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>78</v>
@@ -19057,10 +19056,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19169,10 +19168,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19283,10 +19282,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19312,16 +19311,16 @@
         <v>130</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19370,7 +19369,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19388,21 +19387,21 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19428,13 +19427,13 @@
         <v>102</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -19484,7 +19483,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19502,21 +19501,21 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19549,7 +19548,7 @@
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -19598,7 +19597,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19616,21 +19615,21 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19656,13 +19655,13 @@
         <v>102</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O150" t="s" s="2">
         <v>269</v>
@@ -19743,10 +19742,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19859,10 +19858,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>354</v>
@@ -19977,10 +19976,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20089,10 +20088,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20203,10 +20202,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20232,16 +20231,16 @@
         <v>130</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>78</v>
@@ -20290,7 +20289,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20308,21 +20307,21 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20348,13 +20347,13 @@
         <v>102</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20404,7 +20403,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20422,21 +20421,21 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20469,7 +20468,7 @@
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -20518,7 +20517,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20536,21 +20535,21 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20576,13 +20575,13 @@
         <v>102</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>269</v>
@@ -20663,10 +20662,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20779,10 +20778,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20808,16 +20807,16 @@
         <v>102</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -20866,7 +20865,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -20884,24 +20883,24 @@
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -20923,19 +20922,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -20984,7 +20983,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>88</v>
@@ -21002,21 +21001,21 @@
         <v>339</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21042,14 +21041,14 @@
         <v>275</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21098,7 +21097,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21116,7 +21115,7 @@
         <v>78</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>78</v>
@@ -21127,10 +21126,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21153,16 +21152,16 @@
         <v>78</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21212,7 +21211,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21224,27 +21223,27 @@
         <v>156</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21353,10 +21352,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21467,13 +21466,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="B166" t="s" s="2">
-        <v>659</v>
-      </c>
       <c r="C166" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>78</v>
@@ -21495,13 +21494,13 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -21581,10 +21580,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21607,16 +21606,16 @@
         <v>89</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -21646,7 +21645,7 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>78</v>
@@ -21664,7 +21663,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -21676,27 +21675,27 @@
         <v>156</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21805,10 +21804,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21919,10 +21918,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21945,19 +21944,19 @@
         <v>89</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>78</v>
@@ -22006,7 +22005,7 @@
         <v>78</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22024,21 +22023,21 @@
         <v>78</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22064,20 +22063,20 @@
         <v>173</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q171" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R171" t="s" s="2">
         <v>78</v>
@@ -22098,13 +22097,13 @@
         <v>78</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>78</v>
@@ -22122,7 +22121,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22140,21 +22139,21 @@
         <v>78</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22180,16 +22179,16 @@
         <v>102</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>78</v>
@@ -22238,7 +22237,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22256,21 +22255,21 @@
         <v>78</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22296,16 +22295,16 @@
         <v>130</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -22354,7 +22353,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -22363,7 +22362,7 @@
         <v>88</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>100</v>
@@ -22372,21 +22371,21 @@
         <v>78</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22412,16 +22411,16 @@
         <v>173</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -22470,7 +22469,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -22488,21 +22487,21 @@
         <v>78</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22525,16 +22524,16 @@
         <v>89</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -22564,7 +22563,7 @@
       </c>
       <c r="Y175" s="2"/>
       <c r="Z175" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>78</v>
@@ -22582,7 +22581,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -22594,27 +22593,27 @@
         <v>156</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22723,10 +22722,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22837,10 +22836,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22863,19 +22862,19 @@
         <v>89</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -22924,7 +22923,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -22942,21 +22941,21 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22982,20 +22981,20 @@
         <v>173</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q179" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="R179" t="s" s="2">
         <v>78</v>
@@ -23016,13 +23015,13 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23040,7 +23039,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23058,21 +23057,21 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23098,16 +23097,16 @@
         <v>102</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -23156,7 +23155,7 @@
         <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -23174,21 +23173,21 @@
         <v>78</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23214,16 +23213,16 @@
         <v>130</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>78</v>
@@ -23272,7 +23271,7 @@
         <v>78</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -23281,7 +23280,7 @@
         <v>88</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>100</v>
@@ -23290,21 +23289,21 @@
         <v>78</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23330,16 +23329,16 @@
         <v>173</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
@@ -23388,7 +23387,7 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -23406,21 +23405,21 @@
         <v>78</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23443,13 +23442,13 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -23500,7 +23499,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -23515,10 +23514,10 @@
         <v>100</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>78</v>
@@ -23529,10 +23528,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23641,10 +23640,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23755,14 +23754,14 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
@@ -23784,10 +23783,10 @@
         <v>109</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N186" t="s" s="2">
         <v>112</v>
@@ -23842,7 +23841,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -23871,10 +23870,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23900,13 +23899,13 @@
         <v>102</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23956,7 +23955,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -23971,7 +23970,7 @@
         <v>100</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>318</v>
@@ -23980,15 +23979,15 @@
         <v>78</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24011,13 +24010,13 @@
         <v>78</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -24068,7 +24067,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24083,16 +24082,16 @@
         <v>100</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
